--- a/Employee_Reports_wi48/Catalino Mendoza Rojas Q0562.xlsx
+++ b/Employee_Reports_wi48/Catalino Mendoza Rojas Q0562.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-135</v>
+        <v>-138</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>-273</v>
+        <v>-276</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-335</v>
+        <v>-338</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-119</v>
+        <v>-122</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-119</v>
+        <v>-122</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1829,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1878,11 +1878,11 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -1927,11 +1927,11 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -1964,11 +1964,11 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2001,11 +2001,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2038,11 +2038,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2136,11 +2136,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2173,11 +2173,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2222,11 +2222,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2259,11 +2259,11 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
